--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814970</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814961</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814945</v>
       </c>
       <c r="B4" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814969</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814963</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814943</v>
       </c>
       <c r="B7" t="n">
-        <v>75075</v>
+        <v>75135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814957</v>
+        <v>126814944</v>
       </c>
       <c r="B8" t="n">
-        <v>77934</v>
+        <v>75135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677462</v>
+        <v>677465</v>
       </c>
       <c r="R8" t="n">
-        <v>7109379</v>
+        <v>7109391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>126814964</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814944</v>
+        <v>126814957</v>
       </c>
       <c r="B10" t="n">
-        <v>75075</v>
+        <v>77994</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677465</v>
+        <v>677462</v>
       </c>
       <c r="R10" t="n">
-        <v>7109391</v>
+        <v>7109379</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126814968</v>
+        <v>126814954</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>80150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677477</v>
+        <v>677469</v>
       </c>
       <c r="R11" t="n">
-        <v>7109411</v>
+        <v>7109383</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,6 +1619,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1645,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126814954</v>
+        <v>126814968</v>
       </c>
       <c r="B12" t="n">
-        <v>80119</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677469</v>
+        <v>677477</v>
       </c>
       <c r="R12" t="n">
-        <v>7109383</v>
+        <v>7109411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1716,11 +1721,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126814962</v>
+        <v>126814974</v>
       </c>
       <c r="B13" t="n">
-        <v>82792</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677473</v>
+        <v>677466</v>
       </c>
       <c r="R13" t="n">
-        <v>7109404</v>
+        <v>7109379</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814974</v>
+        <v>126814962</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>82852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,39 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677466</v>
+        <v>677473</v>
       </c>
       <c r="R14" t="n">
-        <v>7109379</v>
+        <v>7109404</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
         <v>126814972</v>
       </c>
       <c r="B15" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126837623</v>
       </c>
       <c r="B16" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126814970</v>
+        <v>126814961</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677462</v>
+        <v>677470</v>
       </c>
       <c r="R2" t="n">
-        <v>7109378</v>
+        <v>7109382</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126814961</v>
+        <v>126814970</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677470</v>
+        <v>677462</v>
       </c>
       <c r="R3" t="n">
-        <v>7109382</v>
+        <v>7109378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>126814945</v>
       </c>
       <c r="B4" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814969</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814963</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814943</v>
       </c>
       <c r="B7" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814944</v>
       </c>
       <c r="B8" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126814964</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126814957</v>
       </c>
       <c r="B10" t="n">
-        <v>77994</v>
+        <v>77997</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126814954</v>
+        <v>126814968</v>
       </c>
       <c r="B11" t="n">
-        <v>80150</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677469</v>
+        <v>677477</v>
       </c>
       <c r="R11" t="n">
-        <v>7109383</v>
+        <v>7109411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126814968</v>
+        <v>126814954</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>80153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677477</v>
+        <v>677469</v>
       </c>
       <c r="R12" t="n">
-        <v>7109411</v>
+        <v>7109383</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1721,6 +1716,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,7 +1852,7 @@
         <v>126814962</v>
       </c>
       <c r="B14" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>126814972</v>
       </c>
       <c r="B15" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126837623</v>
       </c>
       <c r="B16" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126814961</v>
+        <v>126814970</v>
       </c>
       <c r="B2" t="n">
         <v>79014</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677470</v>
+        <v>677462</v>
       </c>
       <c r="R2" t="n">
-        <v>7109382</v>
+        <v>7109378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126814970</v>
+        <v>126814961</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677462</v>
+        <v>677470</v>
       </c>
       <c r="R3" t="n">
-        <v>7109378</v>
+        <v>7109382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126814974</v>
+        <v>126814962</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>82855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,39 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677466</v>
+        <v>677473</v>
       </c>
       <c r="R13" t="n">
-        <v>7109379</v>
+        <v>7109404</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814962</v>
+        <v>126814974</v>
       </c>
       <c r="B14" t="n">
-        <v>82855</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,34 +1855,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677473</v>
+        <v>677466</v>
       </c>
       <c r="R14" t="n">
-        <v>7109404</v>
+        <v>7109379</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814969</v>
+        <v>126814963</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677470</v>
+        <v>677414</v>
       </c>
       <c r="R5" t="n">
-        <v>7109386</v>
+        <v>7109372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814963</v>
+        <v>126814969</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677414</v>
+        <v>677470</v>
       </c>
       <c r="R6" t="n">
-        <v>7109372</v>
+        <v>7109386</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814944</v>
+        <v>126814964</v>
       </c>
       <c r="B8" t="n">
-        <v>75138</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677465</v>
+        <v>677401</v>
       </c>
       <c r="R8" t="n">
         <v>7109391</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814964</v>
+        <v>126814944</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>75138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677401</v>
+        <v>677465</v>
       </c>
       <c r="R9" t="n">
         <v>7109391</v>
@@ -1949,7 +1949,7 @@
         <v>126814972</v>
       </c>
       <c r="B15" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126837623</v>
       </c>
       <c r="B16" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126814962</v>
+        <v>126814974</v>
       </c>
       <c r="B13" t="n">
-        <v>82855</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677473</v>
+        <v>677466</v>
       </c>
       <c r="R13" t="n">
-        <v>7109404</v>
+        <v>7109379</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814974</v>
+        <v>126814962</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>82855</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,39 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677466</v>
+        <v>677473</v>
       </c>
       <c r="R14" t="n">
-        <v>7109379</v>
+        <v>7109404</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126814970</v>
+        <v>126814961</v>
       </c>
       <c r="B2" t="n">
         <v>79014</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677462</v>
+        <v>677470</v>
       </c>
       <c r="R2" t="n">
-        <v>7109378</v>
+        <v>7109382</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126814961</v>
+        <v>126814970</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677470</v>
+        <v>677462</v>
       </c>
       <c r="R3" t="n">
-        <v>7109382</v>
+        <v>7109378</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814963</v>
+        <v>126814969</v>
       </c>
       <c r="B5" t="n">
         <v>79014</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677414</v>
+        <v>677470</v>
       </c>
       <c r="R5" t="n">
-        <v>7109372</v>
+        <v>7109386</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814969</v>
+        <v>126814963</v>
       </c>
       <c r="B6" t="n">
         <v>79014</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677470</v>
+        <v>677414</v>
       </c>
       <c r="R6" t="n">
-        <v>7109386</v>
+        <v>7109372</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814964</v>
+        <v>126814957</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>77997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677401</v>
+        <v>677462</v>
       </c>
       <c r="R8" t="n">
-        <v>7109391</v>
+        <v>7109379</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814957</v>
+        <v>126814964</v>
       </c>
       <c r="B10" t="n">
-        <v>77997</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677462</v>
+        <v>677401</v>
       </c>
       <c r="R10" t="n">
-        <v>7109379</v>
+        <v>7109391</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126814974</v>
+        <v>126814962</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>82855</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,39 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677466</v>
+        <v>677473</v>
       </c>
       <c r="R13" t="n">
-        <v>7109379</v>
+        <v>7109404</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814962</v>
+        <v>126814974</v>
       </c>
       <c r="B14" t="n">
-        <v>82855</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,34 +1855,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677473</v>
+        <v>677466</v>
       </c>
       <c r="R14" t="n">
-        <v>7109404</v>
+        <v>7109379</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126814961</v>
+        <v>126814970</v>
       </c>
       <c r="B2" t="n">
         <v>79014</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>677470</v>
+        <v>677462</v>
       </c>
       <c r="R2" t="n">
-        <v>7109382</v>
+        <v>7109378</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126814970</v>
+        <v>126814961</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>677462</v>
+        <v>677470</v>
       </c>
       <c r="R3" t="n">
-        <v>7109378</v>
+        <v>7109382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814970</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814961</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814945</v>
       </c>
       <c r="B4" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814969</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814963</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814943</v>
       </c>
       <c r="B7" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814957</v>
+        <v>126814964</v>
       </c>
       <c r="B8" t="n">
-        <v>77997</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677462</v>
+        <v>677401</v>
       </c>
       <c r="R8" t="n">
-        <v>7109379</v>
+        <v>7109391</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>126814944</v>
       </c>
       <c r="B9" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126814964</v>
+        <v>126814957</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>78001</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>677401</v>
+        <v>677462</v>
       </c>
       <c r="R10" t="n">
-        <v>7109391</v>
+        <v>7109379</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126814968</v>
+        <v>126814954</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>80157</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677477</v>
+        <v>677469</v>
       </c>
       <c r="R11" t="n">
-        <v>7109411</v>
+        <v>7109383</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,6 +1619,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1645,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126814954</v>
+        <v>126814968</v>
       </c>
       <c r="B12" t="n">
-        <v>80153</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677469</v>
+        <v>677477</v>
       </c>
       <c r="R12" t="n">
-        <v>7109383</v>
+        <v>7109411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1716,11 +1721,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1750,7 +1750,7 @@
         <v>126814962</v>
       </c>
       <c r="B13" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>126814974</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>126814972</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126837623</v>
       </c>
       <c r="B16" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814969</v>
+        <v>126814963</v>
       </c>
       <c r="B5" t="n">
         <v>79018</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677470</v>
+        <v>677414</v>
       </c>
       <c r="R5" t="n">
-        <v>7109386</v>
+        <v>7109372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814963</v>
+        <v>126814969</v>
       </c>
       <c r="B6" t="n">
         <v>79018</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677414</v>
+        <v>677470</v>
       </c>
       <c r="R6" t="n">
-        <v>7109372</v>
+        <v>7109386</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126814964</v>
+        <v>126814944</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>75142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>677401</v>
+        <v>677465</v>
       </c>
       <c r="R8" t="n">
         <v>7109391</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126814944</v>
+        <v>126814964</v>
       </c>
       <c r="B9" t="n">
-        <v>75142</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,7 +1389,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>677465</v>
+        <v>677401</v>
       </c>
       <c r="R9" t="n">
         <v>7109391</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126814954</v>
+        <v>126814968</v>
       </c>
       <c r="B11" t="n">
-        <v>80157</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677469</v>
+        <v>677477</v>
       </c>
       <c r="R11" t="n">
-        <v>7109383</v>
+        <v>7109411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126814968</v>
+        <v>126814954</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>80157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677477</v>
+        <v>677469</v>
       </c>
       <c r="R12" t="n">
-        <v>7109411</v>
+        <v>7109383</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1721,6 +1716,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126814963</v>
+        <v>126814969</v>
       </c>
       <c r="B5" t="n">
         <v>79018</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>677414</v>
+        <v>677470</v>
       </c>
       <c r="R5" t="n">
-        <v>7109372</v>
+        <v>7109386</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126814969</v>
+        <v>126814963</v>
       </c>
       <c r="B6" t="n">
         <v>79018</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>677470</v>
+        <v>677414</v>
       </c>
       <c r="R6" t="n">
-        <v>7109386</v>
+        <v>7109372</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -2046,7 +2046,7 @@
         <v>126837623</v>
       </c>
       <c r="B16" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814970</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814961</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814945</v>
       </c>
       <c r="B4" t="n">
-        <v>75142</v>
+        <v>75135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814969</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814963</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814943</v>
       </c>
       <c r="B7" t="n">
-        <v>75142</v>
+        <v>75135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814944</v>
       </c>
       <c r="B8" t="n">
-        <v>75142</v>
+        <v>75135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126814964</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126814957</v>
       </c>
       <c r="B10" t="n">
-        <v>78001</v>
+        <v>77994</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126814968</v>
+        <v>126814954</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677477</v>
+        <v>677469</v>
       </c>
       <c r="R11" t="n">
-        <v>7109411</v>
+        <v>7109383</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,6 +1619,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1645,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126814954</v>
+        <v>126814968</v>
       </c>
       <c r="B12" t="n">
-        <v>80157</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677469</v>
+        <v>677477</v>
       </c>
       <c r="R12" t="n">
-        <v>7109383</v>
+        <v>7109411</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1716,11 +1721,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126814962</v>
+        <v>126814974</v>
       </c>
       <c r="B13" t="n">
-        <v>82859</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,34 +1758,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677473</v>
+        <v>677466</v>
       </c>
       <c r="R13" t="n">
-        <v>7109404</v>
+        <v>7109379</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814974</v>
+        <v>126814962</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>82852</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,39 +1860,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677466</v>
+        <v>677473</v>
       </c>
       <c r="R14" t="n">
-        <v>7109379</v>
+        <v>7109404</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
         <v>126814972</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126837623</v>
       </c>
       <c r="B16" t="n">
-        <v>98469</v>
+        <v>98457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 26792-2025 artfynd.xlsx
+++ b/artfynd/A 26792-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126814970</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126814961</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126814945</v>
       </c>
       <c r="B4" t="n">
-        <v>75135</v>
+        <v>75142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126814969</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126814963</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126814943</v>
       </c>
       <c r="B7" t="n">
-        <v>75135</v>
+        <v>75142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126814944</v>
       </c>
       <c r="B8" t="n">
-        <v>75135</v>
+        <v>75142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126814964</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126814957</v>
       </c>
       <c r="B10" t="n">
-        <v>77994</v>
+        <v>78001</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126814954</v>
+        <v>126814968</v>
       </c>
       <c r="B11" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>677469</v>
+        <v>677477</v>
       </c>
       <c r="R11" t="n">
-        <v>7109383</v>
+        <v>7109411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1619,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126814968</v>
+        <v>126814954</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>80157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>677477</v>
+        <v>677469</v>
       </c>
       <c r="R12" t="n">
-        <v>7109411</v>
+        <v>7109383</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1721,6 +1716,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På grov gammal rönn</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126814974</v>
+        <v>126814962</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>82859</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,39 +1758,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>677466</v>
+        <v>677473</v>
       </c>
       <c r="R13" t="n">
-        <v>7109379</v>
+        <v>7109404</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1849,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126814962</v>
+        <v>126814974</v>
       </c>
       <c r="B14" t="n">
-        <v>82852</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1860,34 +1855,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storaggan, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>677473</v>
+        <v>677466</v>
       </c>
       <c r="R14" t="n">
-        <v>7109404</v>
+        <v>7109379</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1949,7 +1949,7 @@
         <v>126814972</v>
       </c>
       <c r="B15" t="n">
-        <v>98353</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,7 +2046,7 @@
         <v>126837623</v>
       </c>
       <c r="B16" t="n">
-        <v>98457</v>
+        <v>98469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
